--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:50</t>
+          <t>2026-09-09 00:50:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:51</t>
+          <t>2026-09-09 00:51:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:53</t>
+          <t>2026-09-09 00:51:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:54</t>
+          <t>2026-09-09 00:51:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:54</t>
+          <t>2026-09-09 00:51:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:54</t>
+          <t>2026-09-09 00:51:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:54</t>
+          <t>2026-09-09 00:51:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:54</t>
+          <t>2026-09-09 00:51:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:59</t>
+          <t>2026-09-09 01:16:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:01</t>
+          <t>2026-09-09 01:16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:02</t>
+          <t>2026-09-09 01:16:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:03</t>
+          <t>2026-09-09 01:16:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:03</t>
+          <t>2026-09-09 01:16:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:03</t>
+          <t>2026-09-09 01:16:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:03</t>
+          <t>2026-09-09 01:16:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:03</t>
+          <t>2026-09-09 01:16:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.65%588,000</t>
+          <t>14.98%637,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.65%</t>
+          <t>14.98%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>588000</v>
+        <v>637000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2376技嘉科技</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.06%357</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>357</v>
+        <v>640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.18%1,215,000</t>
+          <t>4.15%706,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1215000</v>
+        <v>706000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>-2.1%349.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>618</v>
+        <v>349.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.14%706,000</t>
+          <t>4.13%1,215,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>706000</v>
+        <v>1215000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.96%104</t>
+          <t>0%104</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.69%3,832,000</t>
+          <t>3.79%3,832,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.72%139</t>
+          <t>+0.36%139.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>139</v>
+        <v>139.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.68%2,828,000</t>
+          <t>3.74%2,828,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.01%67,000</t>
+          <t>3.00%67,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.38%657</t>
+          <t>-0.61%653</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.85%444,000</t>
+          <t>2.78%444,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.70%52,000</t>
+          <t>2.64%52,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.68%114,036</t>
+          <t>2.54%114,036</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.76%251.5</t>
+          <t>+0.2%252</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.47%1,021,000</t>
+          <t>2.45%1,021,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,25 +1114,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+0.29%1700</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>954</v>
+        <v>1700</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.26%252,000</t>
+          <t>2.26%140,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>252000</v>
+        <v>140000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>1504東元電機</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.29%1695</t>
+          <t>+0.71%70.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1695</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.25%140,000</t>
+          <t>1.95%2,904,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>140000</v>
+        <v>2904000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7750新代科技</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.53%2315</t>
+          <t>-4.27%1345</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2315</v>
+        <v>1345</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.06%92,000</t>
+          <t>1.85%138,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>92000</v>
+        <v>138000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,34 +1297,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3661世芯電子</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.25%4030</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4030</v>
+        <v>1795</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.02%53,000</t>
+          <t>1.80%105,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>53000</v>
+        <v>105000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:28</t>
+          <t>2026-09-09 19:33:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1504東元電機</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.81%70.4</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>70.40000000000001</v>
+        <v>993</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.96%2,904,000</t>
+          <t>1.80%198,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2904000</v>
+        <v>198000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>3661世芯電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>-3.1%3905</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1955</v>
+        <v>3905</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.92%97,000</t>
+          <t>1.80%47,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>97000</v>
+        <v>47000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>2377微星科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.62%156.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1935</v>
+        <v>156.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.84%94,000</t>
+          <t>1.76%1,213,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>94000</v>
+        <v>1213000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-1.94%2270</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1805</v>
+        <v>2270</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.83%105,000</t>
+          <t>1.76%80,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>105000</v>
+        <v>80000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2377微星科技</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.79%152.5</t>
+          <t>-0.73%20.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>152.5</v>
+        <v>20.45</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%1,213,000</t>
+          <t>1.72%8,783,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1213000</v>
+        <v>8783000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+6.04%1405</t>
+          <t>-2.35%66.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1405</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.73%138,000</t>
+          <t>1.72%2,652,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>138000</v>
+        <v>2652000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.73%20.6</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.6</v>
+        <v>3380</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.69%8,783,000</t>
+          <t>1.63%52,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8783000</v>
+        <v>52000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3285</v>
+        <v>565</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.68%52,000</t>
+          <t>1.59%295,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>52000</v>
+        <v>295000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>+2.18%234</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>567</v>
+        <v>234</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.64%295,000</t>
+          <t>1.58%726,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>295000</v>
+        <v>726000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.72%229</t>
+          <t>-2.35%1455</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>229</v>
+        <v>1455</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.60%726,000</t>
+          <t>1.52%107,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>726000</v>
+        <v>107000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.32%1490</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1490</v>
+        <v>2015</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.52%107,000</t>
+          <t>1.49%80,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>107000</v>
+        <v>80000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.33%149</t>
+          <t>-1.34%147</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.19%68.2</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>68.2</v>
+        <v>1975</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.38%2,178,000</t>
+          <t>1.36%74,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2178000</v>
+        <v>74000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.65%955</t>
+          <t>0%955</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.31%143,000</t>
+          <t>1.30%143,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>-0.91%76</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1025</v>
+        <v>76</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.24%125,000</t>
+          <t>1.21%1,657,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>125000</v>
+        <v>1657000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:30</t>
+          <t>2026-09-09 19:33:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.99%76.7</t>
+          <t>-3.59%6720</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>76.7</v>
+        <v>6720</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.18%1,657,000</t>
+          <t>1.19%18,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1657000</v>
+        <v>18000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+6.17%6970</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+6.17%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6970</v>
+        <v>1110</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.11%18,000</t>
+          <t>1.00%102,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>18000</v>
+        <v>102000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,33 +2400,33 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.08%804,000</t>
+          <t>1.00%766,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>804000</v>
+        <v>766000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>-1.52%48.6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1385</v>
+        <v>48.6</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.00%77,000</t>
+          <t>0.99%2,097,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>77000</v>
+        <v>2097000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.51%49.35</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>49.35</v>
+        <v>2335</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.97%2,097,000</t>
+          <t>0.93%43,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2097000</v>
+        <v>43000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5550</v>
+        <v>1345</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.96%18,000</t>
+          <t>0.89%76,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>18000</v>
+        <v>76000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.36%186.5</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>186.5</v>
+        <v>1330</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.93%517,000</t>
+          <t>0.79%60,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>517000</v>
+        <v>60000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+6.17%198</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+6.17%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2265</v>
+        <v>198</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.90%43,000</t>
+          <t>0.69%390,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>43000</v>
+        <v>390000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1225</v>
+        <v>5760</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.89%76,000</t>
+          <t>0.69%13,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>76000</v>
+        <v>13000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.25%65.1</t>
+          <t>+2.46%66.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>65.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.69%1,103,000</t>
+          <t>0.68%1,103,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,33 +2888,33 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.64%22,000</t>
+          <t>0.46%17,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>22000</v>
+        <v>17000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>-2.66%183</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>531</v>
+        <v>183</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.51%105,000</t>
+          <t>0.44%243,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>105000</v>
+        <v>243000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+4.44%188</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>188</v>
+        <v>523</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.41%243,000</t>
+          <t>0.40%79,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>243000</v>
+        <v>79000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+3.13%2635</t>
+          <t>-3.04%2555</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2635</v>
+        <v>2555</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.29%12,000</t>
+          <t>0.30%12,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.13%1,000</t>
+          <t>0.12%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:31</t>
+          <t>2026-09-09 19:33:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:32</t>
+          <t>2026-09-09 19:33:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.48%2085</t>
+          <t>0%2085</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:32</t>
+          <t>2026-09-09 19:33:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.6%800</t>
+          <t>+1.5%812</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:32</t>
+          <t>2026-09-09 19:33:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2%441.5</t>
+          <t>+5.1%464</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>+5.1%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>441.5</v>
+        <v>464</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:32</t>
+          <t>2026-09-09 19:33:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:32</t>
+          <t>2026-09-09 19:33:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.56%189.5</t>
+          <t>+1.06%191.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>189.5</v>
+        <v>191.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:38</t>
+          <t>2026-09-09 22:37:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:39</t>
+          <t>2026-09-09 22:37:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:41</t>
+          <t>2026-09-09 22:37:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:42</t>
+          <t>2026-09-09 22:37:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:42</t>
+          <t>2026-09-09 22:37:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:42</t>
+          <t>2026-09-09 22:37:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:42</t>
+          <t>2026-09-09 22:37:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:42</t>
+          <t>2026-09-09 22:37:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:03</t>
+          <t>2026-09-09 22:48:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:05</t>
+          <t>2026-09-09 22:48:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:06</t>
+          <t>2026-09-09 22:49:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:07</t>
+          <t>2026-09-09 22:49:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:07</t>
+          <t>2026-09-09 22:49:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:07</t>
+          <t>2026-09-09 22:49:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:07</t>
+          <t>2026-09-09 22:49:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:07</t>
+          <t>2026-09-09 22:49:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:57</t>
+          <t>2026-09-09 23:10:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:48:58</t>
+          <t>2026-09-09 23:10:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:00</t>
+          <t>2026-09-09 23:10:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:01</t>
+          <t>2026-09-09 23:10:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:01</t>
+          <t>2026-09-09 23:10:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:01</t>
+          <t>2026-09-09 23:10:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:01</t>
+          <t>2026-09-09 23:10:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:01</t>
+          <t>2026-09-09 23:10:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
